--- a/public/samples/es/sample1.xlsx
+++ b/public/samples/es/sample1.xlsx
@@ -35,7 +35,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -77,10 +79,11 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,8 +514,8 @@
       <c r="C3" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D3" s="2" t="str">
-        <v>6.0</v>
+      <c r="D3" s="3">
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="str">
         <v/>
@@ -537,7 +540,7 @@
       <c r="C4" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>5.6</v>
       </c>
       <c r="E4" s="2" t="str">
@@ -563,7 +566,7 @@
       <c r="C5" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>5.4</v>
       </c>
       <c r="E5" s="2" t="str">
@@ -589,7 +592,7 @@
       <c r="C6" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>6.1</v>
       </c>
       <c r="E6" s="2" t="str">
@@ -615,7 +618,7 @@
       <c r="C7" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>5.9</v>
       </c>
       <c r="E7" s="2" t="str">
@@ -641,7 +644,7 @@
       <c r="C8" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>5.5</v>
       </c>
       <c r="E8" s="2" t="str">
@@ -667,7 +670,7 @@
       <c r="C9" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>5.6</v>
       </c>
       <c r="E9" s="2" t="str">
@@ -693,7 +696,7 @@
       <c r="C10" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <v>5.2</v>
       </c>
       <c r="E10" s="2" t="str">
@@ -719,7 +722,7 @@
       <c r="C11" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="3">
         <v>5.9</v>
       </c>
       <c r="E11" s="2" t="str">
@@ -745,7 +748,7 @@
       <c r="C12" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="3">
         <v>5.7</v>
       </c>
       <c r="E12" s="2" t="str">
@@ -771,7 +774,7 @@
       <c r="C13" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="3">
         <v>5.2</v>
       </c>
       <c r="E13" s="2" t="str">
@@ -797,7 +800,7 @@
       <c r="C14" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="3">
         <v>5.4</v>
       </c>
       <c r="E14" s="2" t="str">
@@ -823,7 +826,7 @@
       <c r="C15" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="3">
         <v>4.9</v>
       </c>
       <c r="E15" s="2" t="str">
@@ -849,7 +852,7 @@
       <c r="C16" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="3">
         <v>6.6</v>
       </c>
       <c r="E16" s="2" t="str">
@@ -875,7 +878,7 @@
       <c r="C17" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>5.9</v>
       </c>
       <c r="E17" s="2" t="str">
@@ -901,7 +904,7 @@
       <c r="C18" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
         <v>5.4</v>
       </c>
       <c r="E18" s="2" t="str">
@@ -927,7 +930,7 @@
       <c r="C19" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="3">
         <v>5.4</v>
       </c>
       <c r="E19" s="2" t="str">
@@ -953,8 +956,8 @@
       <c r="C20" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D20" s="2" t="str">
-        <v>6.0</v>
+      <c r="D20" s="3">
+        <v>6</v>
       </c>
       <c r="E20" s="2" t="str">
         <v/>
@@ -979,7 +982,7 @@
       <c r="C21" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
         <v>5.6</v>
       </c>
       <c r="E21" s="2" t="str">
@@ -1005,7 +1008,7 @@
       <c r="C22" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="3">
         <v>4.4</v>
       </c>
       <c r="E22" s="2" t="str">
@@ -1031,7 +1034,7 @@
       <c r="C23" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="3">
         <v>5.4</v>
       </c>
       <c r="E23" s="2" t="str">
@@ -1057,7 +1060,7 @@
       <c r="C24" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="3">
         <v>5.3</v>
       </c>
       <c r="E24" s="2" t="str">
@@ -1083,7 +1086,7 @@
       <c r="C25" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="3">
         <v>5.4</v>
       </c>
       <c r="E25" s="2" t="str">
@@ -1109,8 +1112,8 @@
       <c r="C26" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D26" s="2" t="str">
-        <v>6.0</v>
+      <c r="D26" s="3">
+        <v>6</v>
       </c>
       <c r="E26" s="2" t="str">
         <v/>
@@ -1135,7 +1138,7 @@
       <c r="C27" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
         <v>5.2</v>
       </c>
       <c r="E27" s="2" t="str">
@@ -1161,7 +1164,7 @@
       <c r="C28" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="3">
         <v>5.3</v>
       </c>
       <c r="E28" s="2" t="str">
@@ -1187,7 +1190,7 @@
       <c r="C29" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="3">
         <v>5.9</v>
       </c>
       <c r="E29" s="2" t="str">
@@ -1213,7 +1216,7 @@
       <c r="C30" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="3">
         <v>5.9</v>
       </c>
       <c r="E30" s="2" t="str">
@@ -1239,7 +1242,7 @@
       <c r="C31" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="3">
         <v>6.2</v>
       </c>
       <c r="E31" s="2" t="str">
@@ -1265,7 +1268,7 @@
       <c r="C32" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="3">
         <v>5.9</v>
       </c>
       <c r="E32" s="2" t="str">
@@ -1291,7 +1294,7 @@
       <c r="C33" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="3">
         <v>4.5</v>
       </c>
       <c r="E33" s="2" t="str">
@@ -1317,7 +1320,7 @@
       <c r="C34" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="3">
         <v>6.3</v>
       </c>
       <c r="E34" s="2" t="str">
@@ -1343,8 +1346,8 @@
       <c r="C35" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D35" s="2" t="str">
-        <v>6.0</v>
+      <c r="D35" s="3">
+        <v>6</v>
       </c>
       <c r="E35" s="2" t="str">
         <v/>
@@ -1369,8 +1372,8 @@
       <c r="C36" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D36" s="2" t="str">
-        <v>5.0</v>
+      <c r="D36" s="3">
+        <v>5</v>
       </c>
       <c r="E36" s="2" t="str">
         <v/>
@@ -1395,7 +1398,7 @@
       <c r="C37" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="3">
         <v>5.1</v>
       </c>
       <c r="E37" s="2" t="str">
@@ -1421,8 +1424,8 @@
       <c r="C38" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D38" s="2" t="str">
-        <v>6.0</v>
+      <c r="D38" s="3">
+        <v>6</v>
       </c>
       <c r="E38" s="2" t="str">
         <v/>
@@ -1447,7 +1450,7 @@
       <c r="C39" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="3">
         <v>5.4</v>
       </c>
       <c r="E39" s="2" t="str">
@@ -1473,7 +1476,7 @@
       <c r="C40" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="3">
         <v>5.9</v>
       </c>
       <c r="E40" s="2" t="str">
@@ -1499,7 +1502,7 @@
       <c r="C41" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="3">
         <v>5.4</v>
       </c>
       <c r="E41" s="2" t="str">
@@ -1525,7 +1528,7 @@
       <c r="C42" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="3">
         <v>6.1</v>
       </c>
       <c r="E42" s="2" t="str">
@@ -1551,7 +1554,7 @@
       <c r="C43" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="3">
         <v>5.9</v>
       </c>
       <c r="E43" s="2" t="str">
@@ -1577,7 +1580,7 @@
       <c r="C44" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="3">
         <v>5.9</v>
       </c>
       <c r="E44" s="2" t="str">
@@ -1603,7 +1606,7 @@
       <c r="C45" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="3">
         <v>5.1</v>
       </c>
       <c r="E45" s="2" t="str">
@@ -1629,7 +1632,7 @@
       <c r="C46" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="3">
         <v>4.8</v>
       </c>
       <c r="E46" s="2" t="str">
@@ -1655,7 +1658,7 @@
       <c r="C47" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="3">
         <v>5.9</v>
       </c>
       <c r="E47" s="2" t="str">
@@ -1681,7 +1684,7 @@
       <c r="C48" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="3">
         <v>5.5</v>
       </c>
       <c r="E48" s="2" t="str">
@@ -1707,7 +1710,7 @@
       <c r="C49" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="3">
         <v>5.5</v>
       </c>
       <c r="E49" s="2" t="str">
@@ -1733,7 +1736,7 @@
       <c r="C50" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="3">
         <v>5.7</v>
       </c>
       <c r="E50" s="2" t="str">
@@ -1759,7 +1762,7 @@
       <c r="C51" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="3">
         <v>5.8</v>
       </c>
       <c r="E51" s="2" t="str">
@@ -1785,7 +1788,7 @@
       <c r="C52" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="3">
         <v>5.6</v>
       </c>
       <c r="E52" s="2" t="str">
@@ -1811,8 +1814,8 @@
       <c r="C53" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D53" s="2" t="str">
-        <v>5.0</v>
+      <c r="D53" s="3">
+        <v>5</v>
       </c>
       <c r="E53" s="2" t="str">
         <v/>
@@ -1837,7 +1840,7 @@
       <c r="C54" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="3">
         <v>5.3</v>
       </c>
       <c r="E54" s="2" t="str">
@@ -1863,7 +1866,7 @@
       <c r="C55" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="3">
         <v>5.4</v>
       </c>
       <c r="E55" s="2" t="str">
@@ -1889,7 +1892,7 @@
       <c r="C56" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="3">
         <v>5.2</v>
       </c>
       <c r="E56" s="2" t="str">
@@ -1915,7 +1918,7 @@
       <c r="C57" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="3">
         <v>6.3</v>
       </c>
       <c r="E57" s="2" t="str">
@@ -1941,7 +1944,7 @@
       <c r="C58" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="3">
         <v>5.2</v>
       </c>
       <c r="E58" s="2" t="str">
@@ -1967,7 +1970,7 @@
       <c r="C59" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="3">
         <v>4.8</v>
       </c>
       <c r="E59" s="2" t="str">
@@ -1993,7 +1996,7 @@
       <c r="C60" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="3">
         <v>4.2</v>
       </c>
       <c r="E60" s="2" t="str">
@@ -2019,7 +2022,7 @@
       <c r="C61" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="3">
         <v>5.4</v>
       </c>
       <c r="E61" s="2" t="str">
@@ -2045,7 +2048,7 @@
       <c r="C62" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="3">
         <v>5.4</v>
       </c>
       <c r="E62" s="2" t="str">
@@ -2071,7 +2074,7 @@
       <c r="C63" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="3">
         <v>6.3</v>
       </c>
       <c r="E63" s="2" t="str">
@@ -2097,7 +2100,7 @@
       <c r="C64" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="3">
         <v>5.5</v>
       </c>
       <c r="E64" s="2" t="str">
@@ -2123,7 +2126,7 @@
       <c r="C65" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="3">
         <v>5.5</v>
       </c>
       <c r="E65" s="2" t="str">
@@ -2149,7 +2152,7 @@
       <c r="C66" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="3">
         <v>5.4</v>
       </c>
       <c r="E66" s="2" t="str">
@@ -2175,8 +2178,8 @@
       <c r="C67" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D67" s="2" t="str">
-        <v>5.0</v>
+      <c r="D67" s="3">
+        <v>5</v>
       </c>
       <c r="E67" s="2" t="str">
         <v/>
@@ -2201,7 +2204,7 @@
       <c r="C68" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="3">
         <v>6.3</v>
       </c>
       <c r="E68" s="2" t="str">
@@ -2227,7 +2230,7 @@
       <c r="C69" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="3">
         <v>5.8</v>
       </c>
       <c r="E69" s="2" t="str">
@@ -2253,7 +2256,7 @@
       <c r="C70" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="3">
         <v>4.8</v>
       </c>
       <c r="E70" s="2" t="str">
@@ -2279,7 +2282,7 @@
       <c r="C71" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="3">
         <v>5.2</v>
       </c>
       <c r="E71" s="2" t="str">
@@ -2305,8 +2308,8 @@
       <c r="C72" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D72" s="2" t="str">
-        <v>6.0</v>
+      <c r="D72" s="3">
+        <v>6</v>
       </c>
       <c r="E72" s="2" t="str">
         <v/>
@@ -2331,7 +2334,7 @@
       <c r="C73" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="3">
         <v>5.1</v>
       </c>
       <c r="E73" s="2" t="str">
@@ -2357,8 +2360,8 @@
       <c r="C74" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D74" s="2" t="str">
-        <v>6.0</v>
+      <c r="D74" s="3">
+        <v>6</v>
       </c>
       <c r="E74" s="2" t="str">
         <v/>
@@ -2383,7 +2386,7 @@
       <c r="C75" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75" s="3">
         <v>5.7</v>
       </c>
       <c r="E75" s="2" t="str">
@@ -2409,7 +2412,7 @@
       <c r="C76" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="3">
         <v>5.5</v>
       </c>
       <c r="E76" s="2" t="str">
@@ -2435,7 +2438,7 @@
       <c r="C77" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="3">
         <v>5.3</v>
       </c>
       <c r="E77" s="2" t="str">
@@ -2461,7 +2464,7 @@
       <c r="C78" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="3">
         <v>5.5</v>
       </c>
       <c r="E78" s="2" t="str">
@@ -2487,7 +2490,7 @@
       <c r="C79" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="3">
         <v>5.8</v>
       </c>
       <c r="E79" s="2" t="str">
@@ -2513,7 +2516,7 @@
       <c r="C80" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="3">
         <v>4.9</v>
       </c>
       <c r="E80" s="2" t="str">
@@ -2539,7 +2542,7 @@
       <c r="C81" s="2" t="str">
         <v>F</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="3">
         <v>5.5</v>
       </c>
       <c r="E81" s="2" t="str">
@@ -2565,7 +2568,7 @@
       <c r="C82" s="2" t="str">
         <v>M</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="3">
         <v>5.4</v>
       </c>
       <c r="E82" s="2" t="str">

--- a/public/samples/es/sample1.xlsx
+++ b/public/samples/es/sample1.xlsx
@@ -492,10 +492,10 @@
         <v>Promedio de notas</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>NEE (PIE)</v>
+        <v>Nivel de lectura</v>
       </c>
       <c r="F2" s="2" t="str">
-        <v>Convivencia escolar</v>
+        <v>Apoyo educativo</v>
       </c>
       <c r="G2" s="2" t="str">
         <v>Liderazgo</v>
@@ -517,11 +517,11 @@
       <c r="D3" s="3">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
+      <c r="E3" s="2">
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G3" s="2" t="str">
         <v/>
@@ -543,11 +543,11 @@
       <c r="D4" s="3">
         <v>5.6</v>
       </c>
-      <c r="E4" s="2" t="str">
-        <v/>
+      <c r="E4" s="2">
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G4" s="2" t="str">
         <v>✓</v>
@@ -569,11 +569,11 @@
       <c r="D5" s="3">
         <v>5.4</v>
       </c>
-      <c r="E5" s="2" t="str">
-        <v/>
+      <c r="E5" s="2">
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G5" s="2" t="str">
         <v/>
@@ -595,11 +595,11 @@
       <c r="D6" s="3">
         <v>6.1</v>
       </c>
-      <c r="E6" s="2" t="str">
-        <v/>
+      <c r="E6" s="2">
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G6" s="2" t="str">
         <v/>
@@ -621,11 +621,11 @@
       <c r="D7" s="3">
         <v>5.9</v>
       </c>
-      <c r="E7" s="2" t="str">
-        <v/>
+      <c r="E7" s="2">
+        <v>4</v>
       </c>
       <c r="F7" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G7" s="2" t="str">
         <v/>
@@ -642,16 +642,16 @@
         <v>Sebastián Castro</v>
       </c>
       <c r="C8" s="2" t="str">
-        <v>M</v>
+        <v>X</v>
       </c>
       <c r="D8" s="3">
         <v>5.5</v>
       </c>
-      <c r="E8" s="2" t="str">
-        <v/>
+      <c r="E8" s="2">
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G8" s="2" t="str">
         <v/>
@@ -673,11 +673,11 @@
       <c r="D9" s="3">
         <v>5.6</v>
       </c>
-      <c r="E9" s="2" t="str">
-        <v/>
+      <c r="E9" s="2">
+        <v>3</v>
       </c>
       <c r="F9" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G9" s="2" t="str">
         <v/>
@@ -699,11 +699,11 @@
       <c r="D10" s="3">
         <v>5.2</v>
       </c>
-      <c r="E10" s="2" t="str">
-        <v/>
+      <c r="E10" s="2">
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G10" s="2" t="str">
         <v/>
@@ -725,11 +725,11 @@
       <c r="D11" s="3">
         <v>5.9</v>
       </c>
-      <c r="E11" s="2" t="str">
-        <v/>
+      <c r="E11" s="2">
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G11" s="2" t="str">
         <v/>
@@ -751,11 +751,11 @@
       <c r="D12" s="3">
         <v>5.7</v>
       </c>
-      <c r="E12" s="2" t="str">
-        <v/>
+      <c r="E12" s="2">
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G12" s="2" t="str">
         <v/>
@@ -777,11 +777,11 @@
       <c r="D13" s="3">
         <v>5.2</v>
       </c>
-      <c r="E13" s="2" t="str">
-        <v/>
+      <c r="E13" s="2">
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G13" s="2" t="str">
         <v/>
@@ -803,11 +803,11 @@
       <c r="D14" s="3">
         <v>5.4</v>
       </c>
-      <c r="E14" s="2" t="str">
-        <v/>
+      <c r="E14" s="2">
+        <v>3</v>
       </c>
       <c r="F14" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G14" s="2" t="str">
         <v/>
@@ -829,11 +829,11 @@
       <c r="D15" s="3">
         <v>4.9</v>
       </c>
-      <c r="E15" s="2" t="str">
-        <v/>
+      <c r="E15" s="2">
+        <v>3</v>
       </c>
       <c r="F15" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G15" s="2" t="str">
         <v/>
@@ -855,11 +855,11 @@
       <c r="D16" s="3">
         <v>6.6</v>
       </c>
-      <c r="E16" s="2" t="str">
-        <v/>
+      <c r="E16" s="2">
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G16" s="2" t="str">
         <v/>
@@ -881,11 +881,11 @@
       <c r="D17" s="3">
         <v>5.9</v>
       </c>
-      <c r="E17" s="2" t="str">
-        <v/>
+      <c r="E17" s="2">
+        <v>2</v>
       </c>
       <c r="F17" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G17" s="2" t="str">
         <v/>
@@ -907,11 +907,11 @@
       <c r="D18" s="3">
         <v>5.4</v>
       </c>
-      <c r="E18" s="2" t="str">
-        <v>✓</v>
+      <c r="E18" s="2">
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G18" s="2" t="str">
         <v/>
@@ -933,11 +933,11 @@
       <c r="D19" s="3">
         <v>5.4</v>
       </c>
-      <c r="E19" s="2" t="str">
-        <v/>
+      <c r="E19" s="2">
+        <v>5</v>
       </c>
       <c r="F19" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G19" s="2" t="str">
         <v/>
@@ -959,11 +959,11 @@
       <c r="D20" s="3">
         <v>6</v>
       </c>
-      <c r="E20" s="2" t="str">
-        <v/>
+      <c r="E20" s="2">
+        <v>5</v>
       </c>
       <c r="F20" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G20" s="2" t="str">
         <v/>
@@ -985,11 +985,11 @@
       <c r="D21" s="3">
         <v>5.6</v>
       </c>
-      <c r="E21" s="2" t="str">
-        <v/>
+      <c r="E21" s="2">
+        <v>4</v>
       </c>
       <c r="F21" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G21" s="2" t="str">
         <v/>
@@ -1011,11 +1011,11 @@
       <c r="D22" s="3">
         <v>4.4</v>
       </c>
-      <c r="E22" s="2" t="str">
-        <v/>
+      <c r="E22" s="2">
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G22" s="2" t="str">
         <v/>
@@ -1037,11 +1037,11 @@
       <c r="D23" s="3">
         <v>5.4</v>
       </c>
-      <c r="E23" s="2" t="str">
-        <v/>
+      <c r="E23" s="2">
+        <v>4</v>
       </c>
       <c r="F23" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G23" s="2" t="str">
         <v/>
@@ -1063,11 +1063,11 @@
       <c r="D24" s="3">
         <v>5.3</v>
       </c>
-      <c r="E24" s="2" t="str">
-        <v/>
+      <c r="E24" s="2">
+        <v>2</v>
       </c>
       <c r="F24" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G24" s="2" t="str">
         <v/>
@@ -1089,11 +1089,11 @@
       <c r="D25" s="3">
         <v>5.4</v>
       </c>
-      <c r="E25" s="2" t="str">
-        <v/>
+      <c r="E25" s="2">
+        <v>4</v>
       </c>
       <c r="F25" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G25" s="2" t="str">
         <v/>
@@ -1115,11 +1115,11 @@
       <c r="D26" s="3">
         <v>6</v>
       </c>
-      <c r="E26" s="2" t="str">
-        <v/>
+      <c r="E26" s="2">
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G26" s="2" t="str">
         <v/>
@@ -1141,11 +1141,11 @@
       <c r="D27" s="3">
         <v>5.2</v>
       </c>
-      <c r="E27" s="2" t="str">
-        <v/>
+      <c r="E27" s="2">
+        <v>4</v>
       </c>
       <c r="F27" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G27" s="2" t="str">
         <v/>
@@ -1167,11 +1167,11 @@
       <c r="D28" s="3">
         <v>5.3</v>
       </c>
-      <c r="E28" s="2" t="str">
-        <v/>
+      <c r="E28" s="2">
+        <v>3</v>
       </c>
       <c r="F28" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G28" s="2" t="str">
         <v>✓</v>
@@ -1193,11 +1193,11 @@
       <c r="D29" s="3">
         <v>5.9</v>
       </c>
-      <c r="E29" s="2" t="str">
-        <v/>
+      <c r="E29" s="2">
+        <v>3</v>
       </c>
       <c r="F29" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G29" s="2" t="str">
         <v/>
@@ -1219,11 +1219,11 @@
       <c r="D30" s="3">
         <v>5.9</v>
       </c>
-      <c r="E30" s="2" t="str">
-        <v/>
+      <c r="E30" s="2">
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G30" s="2" t="str">
         <v/>
@@ -1245,11 +1245,11 @@
       <c r="D31" s="3">
         <v>6.2</v>
       </c>
-      <c r="E31" s="2" t="str">
-        <v/>
+      <c r="E31" s="2">
+        <v>5</v>
       </c>
       <c r="F31" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G31" s="2" t="str">
         <v/>
@@ -1271,11 +1271,11 @@
       <c r="D32" s="3">
         <v>5.9</v>
       </c>
-      <c r="E32" s="2" t="str">
-        <v/>
+      <c r="E32" s="2">
+        <v>4</v>
       </c>
       <c r="F32" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G32" s="2" t="str">
         <v/>
@@ -1297,11 +1297,11 @@
       <c r="D33" s="3">
         <v>4.5</v>
       </c>
-      <c r="E33" s="2" t="str">
-        <v/>
+      <c r="E33" s="2">
+        <v>4</v>
       </c>
       <c r="F33" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G33" s="2" t="str">
         <v/>
@@ -1318,16 +1318,16 @@
         <v>Samuel Flores</v>
       </c>
       <c r="C34" s="2" t="str">
-        <v>M</v>
+        <v>X</v>
       </c>
       <c r="D34" s="3">
         <v>6.3</v>
       </c>
-      <c r="E34" s="2" t="str">
-        <v/>
+      <c r="E34" s="2">
+        <v>3</v>
       </c>
       <c r="F34" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G34" s="2" t="str">
         <v/>
@@ -1349,11 +1349,11 @@
       <c r="D35" s="3">
         <v>6</v>
       </c>
-      <c r="E35" s="2" t="str">
-        <v/>
+      <c r="E35" s="2">
+        <v>1</v>
       </c>
       <c r="F35" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G35" s="2" t="str">
         <v/>
@@ -1375,11 +1375,11 @@
       <c r="D36" s="3">
         <v>5</v>
       </c>
-      <c r="E36" s="2" t="str">
-        <v/>
+      <c r="E36" s="2">
+        <v>3</v>
       </c>
       <c r="F36" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G36" s="2" t="str">
         <v/>
@@ -1401,11 +1401,11 @@
       <c r="D37" s="3">
         <v>5.1</v>
       </c>
-      <c r="E37" s="2" t="str">
-        <v/>
+      <c r="E37" s="2">
+        <v>3</v>
       </c>
       <c r="F37" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G37" s="2" t="str">
         <v/>
@@ -1427,11 +1427,11 @@
       <c r="D38" s="3">
         <v>6</v>
       </c>
-      <c r="E38" s="2" t="str">
-        <v/>
+      <c r="E38" s="2">
+        <v>2</v>
       </c>
       <c r="F38" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G38" s="2" t="str">
         <v/>
@@ -1453,11 +1453,11 @@
       <c r="D39" s="3">
         <v>5.4</v>
       </c>
-      <c r="E39" s="2" t="str">
-        <v/>
+      <c r="E39" s="2">
+        <v>2</v>
       </c>
       <c r="F39" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G39" s="2" t="str">
         <v/>
@@ -1479,11 +1479,11 @@
       <c r="D40" s="3">
         <v>5.9</v>
       </c>
-      <c r="E40" s="2" t="str">
-        <v/>
+      <c r="E40" s="2">
+        <v>3</v>
       </c>
       <c r="F40" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G40" s="2" t="str">
         <v/>
@@ -1505,11 +1505,11 @@
       <c r="D41" s="3">
         <v>5.4</v>
       </c>
-      <c r="E41" s="2" t="str">
-        <v/>
+      <c r="E41" s="2">
+        <v>3</v>
       </c>
       <c r="F41" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G41" s="2" t="str">
         <v/>
@@ -1531,11 +1531,11 @@
       <c r="D42" s="3">
         <v>6.1</v>
       </c>
-      <c r="E42" s="2" t="str">
-        <v/>
+      <c r="E42" s="2">
+        <v>3</v>
       </c>
       <c r="F42" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G42" s="2" t="str">
         <v/>
@@ -1557,11 +1557,11 @@
       <c r="D43" s="3">
         <v>5.9</v>
       </c>
-      <c r="E43" s="2" t="str">
-        <v/>
+      <c r="E43" s="2">
+        <v>5</v>
       </c>
       <c r="F43" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G43" s="2" t="str">
         <v/>
@@ -1583,11 +1583,11 @@
       <c r="D44" s="3">
         <v>5.9</v>
       </c>
-      <c r="E44" s="2" t="str">
-        <v/>
+      <c r="E44" s="2">
+        <v>4</v>
       </c>
       <c r="F44" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G44" s="2" t="str">
         <v>✓</v>
@@ -1609,11 +1609,11 @@
       <c r="D45" s="3">
         <v>5.1</v>
       </c>
-      <c r="E45" s="2" t="str">
-        <v/>
+      <c r="E45" s="2">
+        <v>3</v>
       </c>
       <c r="F45" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G45" s="2" t="str">
         <v/>
@@ -1635,11 +1635,11 @@
       <c r="D46" s="3">
         <v>4.8</v>
       </c>
-      <c r="E46" s="2" t="str">
-        <v/>
+      <c r="E46" s="2">
+        <v>4</v>
       </c>
       <c r="F46" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G46" s="2" t="str">
         <v/>
@@ -1661,11 +1661,11 @@
       <c r="D47" s="3">
         <v>5.9</v>
       </c>
-      <c r="E47" s="2" t="str">
-        <v>✓</v>
+      <c r="E47" s="2">
+        <v>1</v>
       </c>
       <c r="F47" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G47" s="2" t="str">
         <v/>
@@ -1687,11 +1687,11 @@
       <c r="D48" s="3">
         <v>5.5</v>
       </c>
-      <c r="E48" s="2" t="str">
-        <v/>
+      <c r="E48" s="2">
+        <v>2</v>
       </c>
       <c r="F48" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G48" s="2" t="str">
         <v/>
@@ -1713,11 +1713,11 @@
       <c r="D49" s="3">
         <v>5.5</v>
       </c>
-      <c r="E49" s="2" t="str">
-        <v/>
+      <c r="E49" s="2">
+        <v>4</v>
       </c>
       <c r="F49" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G49" s="2" t="str">
         <v/>
@@ -1739,11 +1739,11 @@
       <c r="D50" s="3">
         <v>5.7</v>
       </c>
-      <c r="E50" s="2" t="str">
-        <v/>
+      <c r="E50" s="2">
+        <v>5</v>
       </c>
       <c r="F50" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G50" s="2" t="str">
         <v/>
@@ -1765,11 +1765,11 @@
       <c r="D51" s="3">
         <v>5.8</v>
       </c>
-      <c r="E51" s="2" t="str">
-        <v/>
+      <c r="E51" s="2">
+        <v>5</v>
       </c>
       <c r="F51" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G51" s="2" t="str">
         <v>✓</v>
@@ -1791,11 +1791,11 @@
       <c r="D52" s="3">
         <v>5.6</v>
       </c>
-      <c r="E52" s="2" t="str">
-        <v/>
+      <c r="E52" s="2">
+        <v>2</v>
       </c>
       <c r="F52" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G52" s="2" t="str">
         <v/>
@@ -1817,11 +1817,11 @@
       <c r="D53" s="3">
         <v>5</v>
       </c>
-      <c r="E53" s="2" t="str">
-        <v/>
+      <c r="E53" s="2">
+        <v>5</v>
       </c>
       <c r="F53" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G53" s="2" t="str">
         <v/>
@@ -1843,11 +1843,11 @@
       <c r="D54" s="3">
         <v>5.3</v>
       </c>
-      <c r="E54" s="2" t="str">
-        <v/>
+      <c r="E54" s="2">
+        <v>5</v>
       </c>
       <c r="F54" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G54" s="2" t="str">
         <v>✓</v>
@@ -1869,11 +1869,11 @@
       <c r="D55" s="3">
         <v>5.4</v>
       </c>
-      <c r="E55" s="2" t="str">
-        <v/>
+      <c r="E55" s="2">
+        <v>3</v>
       </c>
       <c r="F55" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G55" s="2" t="str">
         <v/>
@@ -1895,11 +1895,11 @@
       <c r="D56" s="3">
         <v>5.2</v>
       </c>
-      <c r="E56" s="2" t="str">
-        <v/>
+      <c r="E56" s="2">
+        <v>4</v>
       </c>
       <c r="F56" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G56" s="2" t="str">
         <v>✓</v>
@@ -1921,11 +1921,11 @@
       <c r="D57" s="3">
         <v>6.3</v>
       </c>
-      <c r="E57" s="2" t="str">
-        <v/>
+      <c r="E57" s="2">
+        <v>3</v>
       </c>
       <c r="F57" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G57" s="2" t="str">
         <v/>
@@ -1947,11 +1947,11 @@
       <c r="D58" s="3">
         <v>5.2</v>
       </c>
-      <c r="E58" s="2" t="str">
-        <v/>
+      <c r="E58" s="2">
+        <v>3</v>
       </c>
       <c r="F58" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G58" s="2" t="str">
         <v>✓</v>
@@ -1973,11 +1973,11 @@
       <c r="D59" s="3">
         <v>4.8</v>
       </c>
-      <c r="E59" s="2" t="str">
-        <v/>
+      <c r="E59" s="2">
+        <v>2</v>
       </c>
       <c r="F59" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G59" s="2" t="str">
         <v/>
@@ -1994,16 +1994,16 @@
         <v>Diego Herrera</v>
       </c>
       <c r="C60" s="2" t="str">
-        <v>M</v>
+        <v>X</v>
       </c>
       <c r="D60" s="3">
         <v>4.2</v>
       </c>
-      <c r="E60" s="2" t="str">
-        <v/>
+      <c r="E60" s="2">
+        <v>3</v>
       </c>
       <c r="F60" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G60" s="2" t="str">
         <v/>
@@ -2025,11 +2025,11 @@
       <c r="D61" s="3">
         <v>5.4</v>
       </c>
-      <c r="E61" s="2" t="str">
-        <v/>
+      <c r="E61" s="2">
+        <v>3</v>
       </c>
       <c r="F61" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G61" s="2" t="str">
         <v/>
@@ -2051,11 +2051,11 @@
       <c r="D62" s="3">
         <v>5.4</v>
       </c>
-      <c r="E62" s="2" t="str">
-        <v/>
+      <c r="E62" s="2">
+        <v>3</v>
       </c>
       <c r="F62" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G62" s="2" t="str">
         <v/>
@@ -2077,11 +2077,11 @@
       <c r="D63" s="3">
         <v>6.3</v>
       </c>
-      <c r="E63" s="2" t="str">
-        <v>✓</v>
+      <c r="E63" s="2">
+        <v>1</v>
       </c>
       <c r="F63" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G63" s="2" t="str">
         <v/>
@@ -2103,11 +2103,11 @@
       <c r="D64" s="3">
         <v>5.5</v>
       </c>
-      <c r="E64" s="2" t="str">
-        <v/>
+      <c r="E64" s="2">
+        <v>2</v>
       </c>
       <c r="F64" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G64" s="2" t="str">
         <v/>
@@ -2129,11 +2129,11 @@
       <c r="D65" s="3">
         <v>5.5</v>
       </c>
-      <c r="E65" s="2" t="str">
-        <v>✓</v>
+      <c r="E65" s="2">
+        <v>1</v>
       </c>
       <c r="F65" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G65" s="2" t="str">
         <v/>
@@ -2155,11 +2155,11 @@
       <c r="D66" s="3">
         <v>5.4</v>
       </c>
-      <c r="E66" s="2" t="str">
-        <v/>
+      <c r="E66" s="2">
+        <v>4</v>
       </c>
       <c r="F66" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G66" s="2" t="str">
         <v/>
@@ -2181,11 +2181,11 @@
       <c r="D67" s="3">
         <v>5</v>
       </c>
-      <c r="E67" s="2" t="str">
-        <v/>
+      <c r="E67" s="2">
+        <v>3</v>
       </c>
       <c r="F67" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G67" s="2" t="str">
         <v/>
@@ -2207,11 +2207,11 @@
       <c r="D68" s="3">
         <v>6.3</v>
       </c>
-      <c r="E68" s="2" t="str">
-        <v/>
+      <c r="E68" s="2">
+        <v>4</v>
       </c>
       <c r="F68" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G68" s="2" t="str">
         <v/>
@@ -2233,11 +2233,11 @@
       <c r="D69" s="3">
         <v>5.8</v>
       </c>
-      <c r="E69" s="2" t="str">
-        <v/>
+      <c r="E69" s="2">
+        <v>3</v>
       </c>
       <c r="F69" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G69" s="2" t="str">
         <v/>
@@ -2259,11 +2259,11 @@
       <c r="D70" s="3">
         <v>4.8</v>
       </c>
-      <c r="E70" s="2" t="str">
-        <v/>
+      <c r="E70" s="2">
+        <v>4</v>
       </c>
       <c r="F70" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G70" s="2" t="str">
         <v/>
@@ -2285,11 +2285,11 @@
       <c r="D71" s="3">
         <v>5.2</v>
       </c>
-      <c r="E71" s="2" t="str">
-        <v/>
+      <c r="E71" s="2">
+        <v>2</v>
       </c>
       <c r="F71" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G71" s="2" t="str">
         <v/>
@@ -2311,11 +2311,11 @@
       <c r="D72" s="3">
         <v>6</v>
       </c>
-      <c r="E72" s="2" t="str">
-        <v/>
+      <c r="E72" s="2">
+        <v>4</v>
       </c>
       <c r="F72" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G72" s="2" t="str">
         <v/>
@@ -2337,11 +2337,11 @@
       <c r="D73" s="3">
         <v>5.1</v>
       </c>
-      <c r="E73" s="2" t="str">
-        <v>✓</v>
+      <c r="E73" s="2">
+        <v>1</v>
       </c>
       <c r="F73" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G73" s="2" t="str">
         <v/>
@@ -2363,11 +2363,11 @@
       <c r="D74" s="3">
         <v>6</v>
       </c>
-      <c r="E74" s="2" t="str">
-        <v/>
+      <c r="E74" s="2">
+        <v>3</v>
       </c>
       <c r="F74" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G74" s="2" t="str">
         <v/>
@@ -2389,11 +2389,11 @@
       <c r="D75" s="3">
         <v>5.7</v>
       </c>
-      <c r="E75" s="2" t="str">
-        <v/>
+      <c r="E75" s="2">
+        <v>2</v>
       </c>
       <c r="F75" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G75" s="2" t="str">
         <v>✓</v>
@@ -2415,11 +2415,11 @@
       <c r="D76" s="3">
         <v>5.5</v>
       </c>
-      <c r="E76" s="2" t="str">
-        <v/>
+      <c r="E76" s="2">
+        <v>3</v>
       </c>
       <c r="F76" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G76" s="2" t="str">
         <v/>
@@ -2441,11 +2441,11 @@
       <c r="D77" s="3">
         <v>5.3</v>
       </c>
-      <c r="E77" s="2" t="str">
-        <v/>
+      <c r="E77" s="2">
+        <v>3</v>
       </c>
       <c r="F77" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G77" s="2" t="str">
         <v/>
@@ -2467,11 +2467,11 @@
       <c r="D78" s="3">
         <v>5.5</v>
       </c>
-      <c r="E78" s="2" t="str">
-        <v/>
+      <c r="E78" s="2">
+        <v>3</v>
       </c>
       <c r="F78" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G78" s="2" t="str">
         <v/>
@@ -2493,11 +2493,11 @@
       <c r="D79" s="3">
         <v>5.8</v>
       </c>
-      <c r="E79" s="2" t="str">
-        <v/>
+      <c r="E79" s="2">
+        <v>4</v>
       </c>
       <c r="F79" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G79" s="2" t="str">
         <v/>
@@ -2519,11 +2519,11 @@
       <c r="D80" s="3">
         <v>4.9</v>
       </c>
-      <c r="E80" s="2" t="str">
-        <v/>
+      <c r="E80" s="2">
+        <v>3</v>
       </c>
       <c r="F80" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G80" s="2" t="str">
         <v/>
@@ -2545,11 +2545,11 @@
       <c r="D81" s="3">
         <v>5.5</v>
       </c>
-      <c r="E81" s="2" t="str">
-        <v/>
+      <c r="E81" s="2">
+        <v>3</v>
       </c>
       <c r="F81" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G81" s="2" t="str">
         <v/>
@@ -2571,11 +2571,11 @@
       <c r="D82" s="3">
         <v>5.4</v>
       </c>
-      <c r="E82" s="2" t="str">
-        <v/>
+      <c r="E82" s="2">
+        <v>3</v>
       </c>
       <c r="F82" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G82" s="2" t="str">
         <v/>

--- a/public/samples/es/sample1.xlsx
+++ b/public/samples/es/sample1.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Lista de estudiantes" sheetId="2" r:id="rId2"/>
     <sheet name="Mantener juntos" sheetId="3" r:id="rId3"/>
     <sheet name="Separar" sheetId="4" r:id="rId4"/>
+    <sheet name="Criterios" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -642,7 +643,7 @@
         <v>Sebastián Castro</v>
       </c>
       <c r="C8" s="2" t="str">
-        <v>X</v>
+        <v>M</v>
       </c>
       <c r="D8" s="3">
         <v>5.5</v>
@@ -850,7 +851,7 @@
         <v>Tomás Torres</v>
       </c>
       <c r="C16" s="2" t="str">
-        <v>M</v>
+        <v>X</v>
       </c>
       <c r="D16" s="3">
         <v>6.6</v>
@@ -1318,7 +1319,7 @@
         <v>Samuel Flores</v>
       </c>
       <c r="C34" s="2" t="str">
-        <v>X</v>
+        <v>M</v>
       </c>
       <c r="D34" s="3">
         <v>6.3</v>
@@ -1552,7 +1553,7 @@
         <v>Sofía López</v>
       </c>
       <c r="C43" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D43" s="3">
         <v>5.9</v>
@@ -1994,7 +1995,7 @@
         <v>Diego Herrera</v>
       </c>
       <c r="C60" s="2" t="str">
-        <v>X</v>
+        <v>M</v>
       </c>
       <c r="D60" s="3">
         <v>4.2</v>
@@ -2228,7 +2229,7 @@
         <v>Paula Flores</v>
       </c>
       <c r="C69" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D69" s="3">
         <v>5.8</v>
@@ -2681,4 +2682,95 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Criterio</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>Opciones</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>Género</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>F</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>M</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <v>X</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>Promedio de notas</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Número</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>Nivel de lectura</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Nivel</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Apoyo educativo</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>Casilla</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>Liderazgo</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>Casilla</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="str">
+        <v>Grupo de origen</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <v>A</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <v>C</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <v>D</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/samples/es/sample1.xlsx
+++ b/public/samples/es/sample1.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Lista de estudiantes" sheetId="2" r:id="rId2"/>
     <sheet name="Mantener juntos" sheetId="3" r:id="rId3"/>
     <sheet name="Separar" sheetId="4" r:id="rId4"/>
+    <sheet name="Criterios" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -492,10 +493,10 @@
         <v>Promedio de notas</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>NEE (PIE)</v>
+        <v>Nivel de lectura</v>
       </c>
       <c r="F2" s="2" t="str">
-        <v>Convivencia escolar</v>
+        <v>Apoyo educativo</v>
       </c>
       <c r="G2" s="2" t="str">
         <v>Liderazgo</v>
@@ -517,11 +518,11 @@
       <c r="D3" s="3">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
+      <c r="E3" s="2">
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G3" s="2" t="str">
         <v/>
@@ -543,11 +544,11 @@
       <c r="D4" s="3">
         <v>5.6</v>
       </c>
-      <c r="E4" s="2" t="str">
-        <v/>
+      <c r="E4" s="2">
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G4" s="2" t="str">
         <v>✓</v>
@@ -569,11 +570,11 @@
       <c r="D5" s="3">
         <v>5.4</v>
       </c>
-      <c r="E5" s="2" t="str">
-        <v/>
+      <c r="E5" s="2">
+        <v>4</v>
       </c>
       <c r="F5" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G5" s="2" t="str">
         <v/>
@@ -595,11 +596,11 @@
       <c r="D6" s="3">
         <v>6.1</v>
       </c>
-      <c r="E6" s="2" t="str">
-        <v/>
+      <c r="E6" s="2">
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G6" s="2" t="str">
         <v/>
@@ -621,11 +622,11 @@
       <c r="D7" s="3">
         <v>5.9</v>
       </c>
-      <c r="E7" s="2" t="str">
-        <v/>
+      <c r="E7" s="2">
+        <v>4</v>
       </c>
       <c r="F7" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G7" s="2" t="str">
         <v/>
@@ -647,11 +648,11 @@
       <c r="D8" s="3">
         <v>5.5</v>
       </c>
-      <c r="E8" s="2" t="str">
-        <v/>
+      <c r="E8" s="2">
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G8" s="2" t="str">
         <v/>
@@ -673,11 +674,11 @@
       <c r="D9" s="3">
         <v>5.6</v>
       </c>
-      <c r="E9" s="2" t="str">
-        <v/>
+      <c r="E9" s="2">
+        <v>3</v>
       </c>
       <c r="F9" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G9" s="2" t="str">
         <v/>
@@ -699,11 +700,11 @@
       <c r="D10" s="3">
         <v>5.2</v>
       </c>
-      <c r="E10" s="2" t="str">
-        <v/>
+      <c r="E10" s="2">
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G10" s="2" t="str">
         <v/>
@@ -725,11 +726,11 @@
       <c r="D11" s="3">
         <v>5.9</v>
       </c>
-      <c r="E11" s="2" t="str">
-        <v/>
+      <c r="E11" s="2">
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G11" s="2" t="str">
         <v/>
@@ -751,11 +752,11 @@
       <c r="D12" s="3">
         <v>5.7</v>
       </c>
-      <c r="E12" s="2" t="str">
-        <v/>
+      <c r="E12" s="2">
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G12" s="2" t="str">
         <v/>
@@ -777,11 +778,11 @@
       <c r="D13" s="3">
         <v>5.2</v>
       </c>
-      <c r="E13" s="2" t="str">
-        <v/>
+      <c r="E13" s="2">
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G13" s="2" t="str">
         <v/>
@@ -803,11 +804,11 @@
       <c r="D14" s="3">
         <v>5.4</v>
       </c>
-      <c r="E14" s="2" t="str">
-        <v/>
+      <c r="E14" s="2">
+        <v>3</v>
       </c>
       <c r="F14" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G14" s="2" t="str">
         <v/>
@@ -829,11 +830,11 @@
       <c r="D15" s="3">
         <v>4.9</v>
       </c>
-      <c r="E15" s="2" t="str">
-        <v/>
+      <c r="E15" s="2">
+        <v>3</v>
       </c>
       <c r="F15" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G15" s="2" t="str">
         <v/>
@@ -850,16 +851,16 @@
         <v>Tomás Torres</v>
       </c>
       <c r="C16" s="2" t="str">
-        <v>M</v>
+        <v>X</v>
       </c>
       <c r="D16" s="3">
         <v>6.6</v>
       </c>
-      <c r="E16" s="2" t="str">
-        <v/>
+      <c r="E16" s="2">
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G16" s="2" t="str">
         <v/>
@@ -881,11 +882,11 @@
       <c r="D17" s="3">
         <v>5.9</v>
       </c>
-      <c r="E17" s="2" t="str">
-        <v/>
+      <c r="E17" s="2">
+        <v>2</v>
       </c>
       <c r="F17" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G17" s="2" t="str">
         <v/>
@@ -907,11 +908,11 @@
       <c r="D18" s="3">
         <v>5.4</v>
       </c>
-      <c r="E18" s="2" t="str">
-        <v>✓</v>
+      <c r="E18" s="2">
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G18" s="2" t="str">
         <v/>
@@ -933,11 +934,11 @@
       <c r="D19" s="3">
         <v>5.4</v>
       </c>
-      <c r="E19" s="2" t="str">
-        <v/>
+      <c r="E19" s="2">
+        <v>5</v>
       </c>
       <c r="F19" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G19" s="2" t="str">
         <v/>
@@ -959,11 +960,11 @@
       <c r="D20" s="3">
         <v>6</v>
       </c>
-      <c r="E20" s="2" t="str">
-        <v/>
+      <c r="E20" s="2">
+        <v>5</v>
       </c>
       <c r="F20" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G20" s="2" t="str">
         <v/>
@@ -985,11 +986,11 @@
       <c r="D21" s="3">
         <v>5.6</v>
       </c>
-      <c r="E21" s="2" t="str">
-        <v/>
+      <c r="E21" s="2">
+        <v>4</v>
       </c>
       <c r="F21" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G21" s="2" t="str">
         <v/>
@@ -1011,11 +1012,11 @@
       <c r="D22" s="3">
         <v>4.4</v>
       </c>
-      <c r="E22" s="2" t="str">
-        <v/>
+      <c r="E22" s="2">
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G22" s="2" t="str">
         <v/>
@@ -1037,11 +1038,11 @@
       <c r="D23" s="3">
         <v>5.4</v>
       </c>
-      <c r="E23" s="2" t="str">
-        <v/>
+      <c r="E23" s="2">
+        <v>4</v>
       </c>
       <c r="F23" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G23" s="2" t="str">
         <v/>
@@ -1063,11 +1064,11 @@
       <c r="D24" s="3">
         <v>5.3</v>
       </c>
-      <c r="E24" s="2" t="str">
-        <v/>
+      <c r="E24" s="2">
+        <v>2</v>
       </c>
       <c r="F24" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G24" s="2" t="str">
         <v/>
@@ -1089,11 +1090,11 @@
       <c r="D25" s="3">
         <v>5.4</v>
       </c>
-      <c r="E25" s="2" t="str">
-        <v/>
+      <c r="E25" s="2">
+        <v>4</v>
       </c>
       <c r="F25" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G25" s="2" t="str">
         <v/>
@@ -1115,11 +1116,11 @@
       <c r="D26" s="3">
         <v>6</v>
       </c>
-      <c r="E26" s="2" t="str">
-        <v/>
+      <c r="E26" s="2">
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G26" s="2" t="str">
         <v/>
@@ -1141,11 +1142,11 @@
       <c r="D27" s="3">
         <v>5.2</v>
       </c>
-      <c r="E27" s="2" t="str">
-        <v/>
+      <c r="E27" s="2">
+        <v>4</v>
       </c>
       <c r="F27" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G27" s="2" t="str">
         <v/>
@@ -1167,11 +1168,11 @@
       <c r="D28" s="3">
         <v>5.3</v>
       </c>
-      <c r="E28" s="2" t="str">
-        <v/>
+      <c r="E28" s="2">
+        <v>3</v>
       </c>
       <c r="F28" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G28" s="2" t="str">
         <v>✓</v>
@@ -1193,11 +1194,11 @@
       <c r="D29" s="3">
         <v>5.9</v>
       </c>
-      <c r="E29" s="2" t="str">
-        <v/>
+      <c r="E29" s="2">
+        <v>3</v>
       </c>
       <c r="F29" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G29" s="2" t="str">
         <v/>
@@ -1219,11 +1220,11 @@
       <c r="D30" s="3">
         <v>5.9</v>
       </c>
-      <c r="E30" s="2" t="str">
-        <v/>
+      <c r="E30" s="2">
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G30" s="2" t="str">
         <v/>
@@ -1245,11 +1246,11 @@
       <c r="D31" s="3">
         <v>6.2</v>
       </c>
-      <c r="E31" s="2" t="str">
-        <v/>
+      <c r="E31" s="2">
+        <v>5</v>
       </c>
       <c r="F31" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G31" s="2" t="str">
         <v/>
@@ -1271,11 +1272,11 @@
       <c r="D32" s="3">
         <v>5.9</v>
       </c>
-      <c r="E32" s="2" t="str">
-        <v/>
+      <c r="E32" s="2">
+        <v>4</v>
       </c>
       <c r="F32" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G32" s="2" t="str">
         <v/>
@@ -1297,11 +1298,11 @@
       <c r="D33" s="3">
         <v>4.5</v>
       </c>
-      <c r="E33" s="2" t="str">
-        <v/>
+      <c r="E33" s="2">
+        <v>4</v>
       </c>
       <c r="F33" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G33" s="2" t="str">
         <v/>
@@ -1323,11 +1324,11 @@
       <c r="D34" s="3">
         <v>6.3</v>
       </c>
-      <c r="E34" s="2" t="str">
-        <v/>
+      <c r="E34" s="2">
+        <v>3</v>
       </c>
       <c r="F34" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G34" s="2" t="str">
         <v/>
@@ -1349,11 +1350,11 @@
       <c r="D35" s="3">
         <v>6</v>
       </c>
-      <c r="E35" s="2" t="str">
-        <v/>
+      <c r="E35" s="2">
+        <v>1</v>
       </c>
       <c r="F35" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G35" s="2" t="str">
         <v/>
@@ -1375,11 +1376,11 @@
       <c r="D36" s="3">
         <v>5</v>
       </c>
-      <c r="E36" s="2" t="str">
-        <v/>
+      <c r="E36" s="2">
+        <v>3</v>
       </c>
       <c r="F36" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G36" s="2" t="str">
         <v/>
@@ -1401,11 +1402,11 @@
       <c r="D37" s="3">
         <v>5.1</v>
       </c>
-      <c r="E37" s="2" t="str">
-        <v/>
+      <c r="E37" s="2">
+        <v>3</v>
       </c>
       <c r="F37" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G37" s="2" t="str">
         <v/>
@@ -1427,11 +1428,11 @@
       <c r="D38" s="3">
         <v>6</v>
       </c>
-      <c r="E38" s="2" t="str">
-        <v/>
+      <c r="E38" s="2">
+        <v>2</v>
       </c>
       <c r="F38" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G38" s="2" t="str">
         <v/>
@@ -1453,11 +1454,11 @@
       <c r="D39" s="3">
         <v>5.4</v>
       </c>
-      <c r="E39" s="2" t="str">
-        <v/>
+      <c r="E39" s="2">
+        <v>2</v>
       </c>
       <c r="F39" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G39" s="2" t="str">
         <v/>
@@ -1479,11 +1480,11 @@
       <c r="D40" s="3">
         <v>5.9</v>
       </c>
-      <c r="E40" s="2" t="str">
-        <v/>
+      <c r="E40" s="2">
+        <v>3</v>
       </c>
       <c r="F40" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G40" s="2" t="str">
         <v/>
@@ -1505,11 +1506,11 @@
       <c r="D41" s="3">
         <v>5.4</v>
       </c>
-      <c r="E41" s="2" t="str">
-        <v/>
+      <c r="E41" s="2">
+        <v>3</v>
       </c>
       <c r="F41" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G41" s="2" t="str">
         <v/>
@@ -1531,11 +1532,11 @@
       <c r="D42" s="3">
         <v>6.1</v>
       </c>
-      <c r="E42" s="2" t="str">
-        <v/>
+      <c r="E42" s="2">
+        <v>3</v>
       </c>
       <c r="F42" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G42" s="2" t="str">
         <v/>
@@ -1552,16 +1553,16 @@
         <v>Sofía López</v>
       </c>
       <c r="C43" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D43" s="3">
         <v>5.9</v>
       </c>
-      <c r="E43" s="2" t="str">
-        <v/>
+      <c r="E43" s="2">
+        <v>5</v>
       </c>
       <c r="F43" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G43" s="2" t="str">
         <v/>
@@ -1583,11 +1584,11 @@
       <c r="D44" s="3">
         <v>5.9</v>
       </c>
-      <c r="E44" s="2" t="str">
-        <v/>
+      <c r="E44" s="2">
+        <v>4</v>
       </c>
       <c r="F44" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G44" s="2" t="str">
         <v>✓</v>
@@ -1609,11 +1610,11 @@
       <c r="D45" s="3">
         <v>5.1</v>
       </c>
-      <c r="E45" s="2" t="str">
-        <v/>
+      <c r="E45" s="2">
+        <v>3</v>
       </c>
       <c r="F45" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G45" s="2" t="str">
         <v/>
@@ -1635,11 +1636,11 @@
       <c r="D46" s="3">
         <v>4.8</v>
       </c>
-      <c r="E46" s="2" t="str">
-        <v/>
+      <c r="E46" s="2">
+        <v>4</v>
       </c>
       <c r="F46" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G46" s="2" t="str">
         <v/>
@@ -1661,11 +1662,11 @@
       <c r="D47" s="3">
         <v>5.9</v>
       </c>
-      <c r="E47" s="2" t="str">
-        <v>✓</v>
+      <c r="E47" s="2">
+        <v>1</v>
       </c>
       <c r="F47" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G47" s="2" t="str">
         <v/>
@@ -1687,11 +1688,11 @@
       <c r="D48" s="3">
         <v>5.5</v>
       </c>
-      <c r="E48" s="2" t="str">
-        <v/>
+      <c r="E48" s="2">
+        <v>2</v>
       </c>
       <c r="F48" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G48" s="2" t="str">
         <v/>
@@ -1713,11 +1714,11 @@
       <c r="D49" s="3">
         <v>5.5</v>
       </c>
-      <c r="E49" s="2" t="str">
-        <v/>
+      <c r="E49" s="2">
+        <v>4</v>
       </c>
       <c r="F49" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G49" s="2" t="str">
         <v/>
@@ -1739,11 +1740,11 @@
       <c r="D50" s="3">
         <v>5.7</v>
       </c>
-      <c r="E50" s="2" t="str">
-        <v/>
+      <c r="E50" s="2">
+        <v>5</v>
       </c>
       <c r="F50" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G50" s="2" t="str">
         <v/>
@@ -1765,11 +1766,11 @@
       <c r="D51" s="3">
         <v>5.8</v>
       </c>
-      <c r="E51" s="2" t="str">
-        <v/>
+      <c r="E51" s="2">
+        <v>5</v>
       </c>
       <c r="F51" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G51" s="2" t="str">
         <v>✓</v>
@@ -1791,11 +1792,11 @@
       <c r="D52" s="3">
         <v>5.6</v>
       </c>
-      <c r="E52" s="2" t="str">
-        <v/>
+      <c r="E52" s="2">
+        <v>2</v>
       </c>
       <c r="F52" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G52" s="2" t="str">
         <v/>
@@ -1817,11 +1818,11 @@
       <c r="D53" s="3">
         <v>5</v>
       </c>
-      <c r="E53" s="2" t="str">
-        <v/>
+      <c r="E53" s="2">
+        <v>5</v>
       </c>
       <c r="F53" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G53" s="2" t="str">
         <v/>
@@ -1843,11 +1844,11 @@
       <c r="D54" s="3">
         <v>5.3</v>
       </c>
-      <c r="E54" s="2" t="str">
-        <v/>
+      <c r="E54" s="2">
+        <v>5</v>
       </c>
       <c r="F54" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G54" s="2" t="str">
         <v>✓</v>
@@ -1869,11 +1870,11 @@
       <c r="D55" s="3">
         <v>5.4</v>
       </c>
-      <c r="E55" s="2" t="str">
-        <v/>
+      <c r="E55" s="2">
+        <v>3</v>
       </c>
       <c r="F55" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G55" s="2" t="str">
         <v/>
@@ -1895,11 +1896,11 @@
       <c r="D56" s="3">
         <v>5.2</v>
       </c>
-      <c r="E56" s="2" t="str">
-        <v/>
+      <c r="E56" s="2">
+        <v>4</v>
       </c>
       <c r="F56" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G56" s="2" t="str">
         <v>✓</v>
@@ -1921,11 +1922,11 @@
       <c r="D57" s="3">
         <v>6.3</v>
       </c>
-      <c r="E57" s="2" t="str">
-        <v/>
+      <c r="E57" s="2">
+        <v>3</v>
       </c>
       <c r="F57" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G57" s="2" t="str">
         <v/>
@@ -1947,11 +1948,11 @@
       <c r="D58" s="3">
         <v>5.2</v>
       </c>
-      <c r="E58" s="2" t="str">
-        <v/>
+      <c r="E58" s="2">
+        <v>3</v>
       </c>
       <c r="F58" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G58" s="2" t="str">
         <v>✓</v>
@@ -1973,11 +1974,11 @@
       <c r="D59" s="3">
         <v>4.8</v>
       </c>
-      <c r="E59" s="2" t="str">
-        <v/>
+      <c r="E59" s="2">
+        <v>2</v>
       </c>
       <c r="F59" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G59" s="2" t="str">
         <v/>
@@ -1999,11 +2000,11 @@
       <c r="D60" s="3">
         <v>4.2</v>
       </c>
-      <c r="E60" s="2" t="str">
-        <v/>
+      <c r="E60" s="2">
+        <v>3</v>
       </c>
       <c r="F60" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G60" s="2" t="str">
         <v/>
@@ -2025,11 +2026,11 @@
       <c r="D61" s="3">
         <v>5.4</v>
       </c>
-      <c r="E61" s="2" t="str">
-        <v/>
+      <c r="E61" s="2">
+        <v>3</v>
       </c>
       <c r="F61" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G61" s="2" t="str">
         <v/>
@@ -2051,11 +2052,11 @@
       <c r="D62" s="3">
         <v>5.4</v>
       </c>
-      <c r="E62" s="2" t="str">
-        <v/>
+      <c r="E62" s="2">
+        <v>3</v>
       </c>
       <c r="F62" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G62" s="2" t="str">
         <v/>
@@ -2077,11 +2078,11 @@
       <c r="D63" s="3">
         <v>6.3</v>
       </c>
-      <c r="E63" s="2" t="str">
-        <v>✓</v>
+      <c r="E63" s="2">
+        <v>1</v>
       </c>
       <c r="F63" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G63" s="2" t="str">
         <v/>
@@ -2103,11 +2104,11 @@
       <c r="D64" s="3">
         <v>5.5</v>
       </c>
-      <c r="E64" s="2" t="str">
-        <v/>
+      <c r="E64" s="2">
+        <v>2</v>
       </c>
       <c r="F64" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G64" s="2" t="str">
         <v/>
@@ -2129,11 +2130,11 @@
       <c r="D65" s="3">
         <v>5.5</v>
       </c>
-      <c r="E65" s="2" t="str">
-        <v>✓</v>
+      <c r="E65" s="2">
+        <v>1</v>
       </c>
       <c r="F65" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G65" s="2" t="str">
         <v/>
@@ -2155,11 +2156,11 @@
       <c r="D66" s="3">
         <v>5.4</v>
       </c>
-      <c r="E66" s="2" t="str">
-        <v/>
+      <c r="E66" s="2">
+        <v>4</v>
       </c>
       <c r="F66" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G66" s="2" t="str">
         <v/>
@@ -2181,11 +2182,11 @@
       <c r="D67" s="3">
         <v>5</v>
       </c>
-      <c r="E67" s="2" t="str">
-        <v/>
+      <c r="E67" s="2">
+        <v>3</v>
       </c>
       <c r="F67" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G67" s="2" t="str">
         <v/>
@@ -2207,11 +2208,11 @@
       <c r="D68" s="3">
         <v>6.3</v>
       </c>
-      <c r="E68" s="2" t="str">
-        <v/>
+      <c r="E68" s="2">
+        <v>4</v>
       </c>
       <c r="F68" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G68" s="2" t="str">
         <v/>
@@ -2228,16 +2229,16 @@
         <v>Paula Flores</v>
       </c>
       <c r="C69" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D69" s="3">
         <v>5.8</v>
       </c>
-      <c r="E69" s="2" t="str">
-        <v/>
+      <c r="E69" s="2">
+        <v>3</v>
       </c>
       <c r="F69" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G69" s="2" t="str">
         <v/>
@@ -2259,11 +2260,11 @@
       <c r="D70" s="3">
         <v>4.8</v>
       </c>
-      <c r="E70" s="2" t="str">
-        <v/>
+      <c r="E70" s="2">
+        <v>4</v>
       </c>
       <c r="F70" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G70" s="2" t="str">
         <v/>
@@ -2285,11 +2286,11 @@
       <c r="D71" s="3">
         <v>5.2</v>
       </c>
-      <c r="E71" s="2" t="str">
-        <v/>
+      <c r="E71" s="2">
+        <v>2</v>
       </c>
       <c r="F71" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G71" s="2" t="str">
         <v/>
@@ -2311,11 +2312,11 @@
       <c r="D72" s="3">
         <v>6</v>
       </c>
-      <c r="E72" s="2" t="str">
-        <v/>
+      <c r="E72" s="2">
+        <v>4</v>
       </c>
       <c r="F72" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G72" s="2" t="str">
         <v/>
@@ -2337,11 +2338,11 @@
       <c r="D73" s="3">
         <v>5.1</v>
       </c>
-      <c r="E73" s="2" t="str">
-        <v>✓</v>
+      <c r="E73" s="2">
+        <v>1</v>
       </c>
       <c r="F73" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G73" s="2" t="str">
         <v/>
@@ -2363,11 +2364,11 @@
       <c r="D74" s="3">
         <v>6</v>
       </c>
-      <c r="E74" s="2" t="str">
-        <v/>
+      <c r="E74" s="2">
+        <v>3</v>
       </c>
       <c r="F74" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G74" s="2" t="str">
         <v/>
@@ -2389,11 +2390,11 @@
       <c r="D75" s="3">
         <v>5.7</v>
       </c>
-      <c r="E75" s="2" t="str">
-        <v/>
+      <c r="E75" s="2">
+        <v>2</v>
       </c>
       <c r="F75" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G75" s="2" t="str">
         <v>✓</v>
@@ -2415,11 +2416,11 @@
       <c r="D76" s="3">
         <v>5.5</v>
       </c>
-      <c r="E76" s="2" t="str">
-        <v/>
+      <c r="E76" s="2">
+        <v>3</v>
       </c>
       <c r="F76" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v>✓</v>
       </c>
       <c r="G76" s="2" t="str">
         <v/>
@@ -2441,11 +2442,11 @@
       <c r="D77" s="3">
         <v>5.3</v>
       </c>
-      <c r="E77" s="2" t="str">
-        <v/>
+      <c r="E77" s="2">
+        <v>3</v>
       </c>
       <c r="F77" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G77" s="2" t="str">
         <v/>
@@ -2467,11 +2468,11 @@
       <c r="D78" s="3">
         <v>5.5</v>
       </c>
-      <c r="E78" s="2" t="str">
-        <v/>
+      <c r="E78" s="2">
+        <v>3</v>
       </c>
       <c r="F78" s="2" t="str">
-        <v>Seguimiento</v>
+        <v/>
       </c>
       <c r="G78" s="2" t="str">
         <v/>
@@ -2493,11 +2494,11 @@
       <c r="D79" s="3">
         <v>5.8</v>
       </c>
-      <c r="E79" s="2" t="str">
-        <v/>
+      <c r="E79" s="2">
+        <v>4</v>
       </c>
       <c r="F79" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G79" s="2" t="str">
         <v/>
@@ -2519,11 +2520,11 @@
       <c r="D80" s="3">
         <v>4.9</v>
       </c>
-      <c r="E80" s="2" t="str">
-        <v/>
+      <c r="E80" s="2">
+        <v>3</v>
       </c>
       <c r="F80" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G80" s="2" t="str">
         <v/>
@@ -2545,11 +2546,11 @@
       <c r="D81" s="3">
         <v>5.5</v>
       </c>
-      <c r="E81" s="2" t="str">
-        <v/>
+      <c r="E81" s="2">
+        <v>3</v>
       </c>
       <c r="F81" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G81" s="2" t="str">
         <v/>
@@ -2571,11 +2572,11 @@
       <c r="D82" s="3">
         <v>5.4</v>
       </c>
-      <c r="E82" s="2" t="str">
-        <v/>
+      <c r="E82" s="2">
+        <v>3</v>
       </c>
       <c r="F82" s="2" t="str">
-        <v>Sin observaciones</v>
+        <v/>
       </c>
       <c r="G82" s="2" t="str">
         <v/>
@@ -2681,4 +2682,95 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Criterio</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>Opciones</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>Género</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>F</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>M</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <v>X</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>Promedio de notas</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Número</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>Nivel de lectura</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Nivel</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Apoyo educativo</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>Casilla</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>Liderazgo</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>Casilla</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="str">
+        <v>Grupo de origen</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>Lista</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <v>A</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <v>C</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <v>D</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+  </ignoredErrors>
+</worksheet>
 </file>